--- a/output/pdf_financials_xlsx/HODL.xlsx
+++ b/output/pdf_financials_xlsx/HODL.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/HODL.xlsx
+++ b/output/pdf_financials_xlsx/HODL.xlsx
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -634,7 +634,7 @@
         <v>8.191922</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>44.810876</v>
+        <v>-44.810876</v>
       </c>
     </row>
     <row r="17">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1.584258</v>
+        <v>-1.584258</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>9.77575</v>
@@ -694,7 +694,7 @@
         <v>6.607664</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>35.035126</v>
+        <v>-35.035126</v>
       </c>
     </row>
     <row r="21">
@@ -733,7 +733,7 @@
         <v>6.607664</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>35.035126</v>
+        <v>-35.035126</v>
       </c>
     </row>
     <row r="24">
@@ -776,15 +776,11 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>18.748605</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>20.092474</v>
       </c>
     </row>
     <row r="27">
@@ -797,7 +793,7 @@
         <v>8.191922</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>44.810876</v>
+        <v>-44.810876</v>
       </c>
     </row>
     <row r="28">
@@ -823,7 +819,7 @@
         <v>8.191922</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>44.810876</v>
+        <v>-44.810876</v>
       </c>
     </row>
     <row r="30">
@@ -853,7 +849,7 @@
         <v>19.33927105262965</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>21.8155744154611</v>
+        <v>-21.8155744154611</v>
       </c>
     </row>
     <row r="32">
@@ -886,15 +882,11 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>1.808052</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>1.785403</v>
       </c>
     </row>
     <row r="35">
@@ -903,15 +895,11 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -920,15 +908,11 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>1.808052</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1.785403</v>
       </c>
     </row>
     <row r="37">
@@ -937,15 +921,11 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0.00675</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0.167151</v>
       </c>
     </row>
     <row r="38">
@@ -954,15 +934,11 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -971,15 +947,11 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -988,15 +960,11 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1005,15 +973,11 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0.00675</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.167151</v>
       </c>
     </row>
     <row r="42">
@@ -1022,15 +986,11 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1039,15 +999,11 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1056,15 +1012,11 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1073,15 +1025,11 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1090,15 +1038,11 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1107,15 +1051,11 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1124,15 +1064,11 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1158,15 +1094,11 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>1.513331</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0.685662</v>
       </c>
     </row>
     <row r="51">
@@ -1175,15 +1107,11 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1192,15 +1120,11 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1209,15 +1133,11 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1226,15 +1146,11 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1260,15 +1176,11 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1277,15 +1189,11 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1294,15 +1202,11 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1311,15 +1215,11 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>38.809125</v>
       </c>
     </row>
     <row r="60">
@@ -1328,15 +1228,11 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1345,15 +1241,11 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1379,15 +1271,11 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>1.814802</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>3.552554</v>
       </c>
     </row>
     <row r="64">
@@ -1396,15 +1284,11 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1413,15 +1297,11 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1430,15 +1310,11 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1447,15 +1323,11 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1464,15 +1336,11 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.232929</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>2.317122</v>
       </c>
     </row>
     <row r="69">
@@ -1481,15 +1349,11 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>16.16459</v>
       </c>
     </row>
     <row r="70">
@@ -1498,15 +1362,11 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1515,15 +1375,11 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>16.16459</v>
       </c>
     </row>
     <row r="72">
@@ -1532,15 +1388,11 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1549,15 +1401,11 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1566,15 +1414,11 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1583,15 +1427,11 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1617,15 +1457,11 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1634,15 +1470,11 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1651,15 +1483,11 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1673,10 +1501,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C80" s="3" t="n">
+        <v>0.1408302669266048</v>
       </c>
     </row>
     <row r="81">
@@ -1685,15 +1511,11 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1702,15 +1524,11 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1719,15 +1537,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0.399406</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0.584981</v>
       </c>
     </row>
     <row r="84">
@@ -1736,15 +1550,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0.399406</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0.584981</v>
       </c>
     </row>
     <row r="85">
@@ -1753,15 +1563,11 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -1787,15 +1593,11 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>1.780615</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>32.959553</v>
       </c>
     </row>
     <row r="88">
@@ -1804,15 +1606,11 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>17.256668</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>70.428555</v>
       </c>
     </row>
     <row r="89">
@@ -1821,15 +1619,11 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1838,15 +1632,11 @@
           <t xml:space="preserve">  Retained Earnings</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B90" s="3" t="n">
+        <v>-10.371011</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>-47.139334</v>
       </c>
     </row>
     <row r="91">
@@ -1855,15 +1645,11 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>2.540513</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>19.049001</v>
       </c>
     </row>
     <row r="92">
@@ -1872,15 +1658,11 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1889,15 +1671,11 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1906,15 +1684,11 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>26.723624</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>114.780653</v>
       </c>
     </row>
     <row r="95">
@@ -1923,15 +1697,11 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1940,15 +1710,11 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>26.723624</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>114.780653</v>
       </c>
     </row>
     <row r="97">
@@ -1957,15 +1723,11 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>14.72536618319795</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>32.30933379197051</v>
       </c>
     </row>
     <row r="98">
@@ -1981,15 +1743,11 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>6.607664</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-35.035126</v>
       </c>
     </row>
     <row r="100">
@@ -1998,15 +1756,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2015,15 +1769,11 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2032,15 +1782,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2049,15 +1795,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0.110388</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>-0.160401</v>
       </c>
     </row>
     <row r="104">
@@ -2066,15 +1808,11 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.080433</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>2.084193</v>
       </c>
     </row>
     <row r="105">
@@ -2083,15 +1821,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2100,15 +1834,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.190821</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>1.923792</v>
       </c>
     </row>
     <row r="107">
@@ -2117,15 +1847,11 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>1.320919</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>7.862418</v>
       </c>
     </row>
     <row r="108">
@@ -2134,15 +1860,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2151,15 +1873,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2168,15 +1886,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2185,15 +1899,11 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2202,15 +1912,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2219,15 +1925,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2236,15 +1938,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2253,15 +1951,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2270,15 +1964,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2287,15 +1977,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2304,15 +1990,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2321,15 +2003,11 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>1.505462</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>-73.196074</v>
       </c>
     </row>
     <row r="120">
@@ -2338,15 +2016,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0.170963</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>1.765033</v>
       </c>
     </row>
     <row r="121">
@@ -2355,15 +2029,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2372,15 +2042,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2389,15 +2055,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2406,15 +2068,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2423,15 +2081,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2440,15 +2094,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2474,15 +2124,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2491,15 +2137,11 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>-0.767961</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>84.176293</v>
       </c>
     </row>
     <row r="130">
@@ -2508,15 +2150,11 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>1.92728</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>1.808052</v>
       </c>
     </row>
     <row r="131">
@@ -2525,15 +2163,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2542,15 +2176,11 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.119228</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-0.022649</v>
       </c>
     </row>
     <row r="133">
@@ -2559,15 +2189,11 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>1.808052</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>1.785403</v>
       </c>
     </row>
     <row r="134">
@@ -2576,15 +2202,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2593,15 +2215,11 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.856729</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-11.002868</v>
       </c>
     </row>
   </sheetData>
@@ -2615,7 +2233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2659,214 +2277,256 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Validation service income - net (note 17) $</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and cash equivalents (note 4) $</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>1.808052</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5.428188</v>
+        <v>1.785403</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Staking rewards (note 17)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Prepaid expenses and accounts receivable (note 5)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="n">
-        <v>0.271245</v>
+        <v>0.00675</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>4.803686</v>
+        <v>0.167151</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Realized (loss) gain on dispositions of cryptocurrencies (note 6)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" s="5" t="n">
-        <v>7.648448</v>
+          <t>Income tax recoverable (note 22)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TaxesReceivable</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>3.948587</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>assets</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Treasury management income</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>assets total</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.814802</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.219775</v>
+        <v>3.552554</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>assets</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dividend income</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>DividendIncome</t>
-        </is>
-      </c>
+          <t>Cryptocurrencies (note 6)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" s="5" t="n">
-        <v>0.322362</v>
+        <v>25.575512</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.138398</v>
+        <v>126.529342</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>assets</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Intangible assets (note 7)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0.148833</v>
+          <t>OtherIntangibleAssets</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.026213</v>
+        <v>38.809125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>assets</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Realized (loss) gain on investments (note 9)</t>
+          <t>Fixed assets (note 8)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" s="5" t="n">
-        <v>1.160891</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.000442</v>
+        <v>0.02032</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>assets</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Unrealized gain on investments (note 9)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Investments (note 9)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
-        <v>1.064911</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.513331</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.685662</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gain from dissolution of subsidiary after tax (note 19)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities (notes 10 and 18) $</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="n">
-        <v>0.076096</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.232929</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.317122</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Realized loss on disposal of assets</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Income tax payable (note 22)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>IncomeTaxPayable</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
-        <v>-0.021759</v>
+        <v>1.547686</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2877,623 +2537,2213 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Impairment losses on intangible assets (note 7)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Credit facility (note 11)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>27.561055</v>
+        <v>16.16459</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amortization (note 7 and 8)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0.031636</v>
+          <t>Convertible debentures (note 12)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>10.20773</v>
+        <v>14.477841</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>liabilities</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Share based compensation (notes 14 and 18)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>liabilities total</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
-        <v>1.320919</v>
+        <v>1.780615</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>7.862418</v>
+        <v>32.959553</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Long-term liabilities</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Professional fees (note 18)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>0.323686</v>
+          <t>Convertible debentures (note 12)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>3.928001</v>
+        <v>21.271816</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Long-term liabilities</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Interest expense and accretion</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deferred tax liability (note 22)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NonCurrentDeferredTaxesLiabilities</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.399406</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>3.197059</v>
+        <v>0.584981</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Long-term liabilities</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Transaction costs (note 12)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Long-term liabilities total</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>2.180021</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>2.380272</v>
+        <v>54.81635</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Consulting fees (note 18)</t>
+          <t>Capital stock (note 13)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.479493</v>
+        <v>17.256668</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1.796827</v>
+        <v>70.428555</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Investor relations</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Reserves (notes 12, 14, 15 and 16)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" s="5" t="n">
+        <v>17.297454</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.853046</v>
+        <v>72.442431</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Accumulated other comprehensive (loss) income</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.344096</v>
+        <v>2.540513</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.768085</v>
+        <v>19.049001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Listing fees</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accumulated deficit</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-10.371011</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.5689689999999999</v>
+        <v>-47.139334</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
+          <t>Shareholders' Equity total</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.050725</v>
+        <v>26.723624</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.163578</v>
+        <v>114.780653</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Director fees (note 18)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Income (loss) for the year $</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
-        <v>0.03</v>
+        <v>6.607664</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.088241</v>
+        <v>-35.035126</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>2.479105</v>
+          <t>Validation service income received in cryptocurrencies</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>59.375281</v>
+        <v>-5.428188</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(Loss) income before taxes (</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>8.191922</v>
+          <t>Validator fees, paid in fiat</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>44.810876</v>
+        <v>-0.575315</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Deferred tax expense (recovery) (note 22)</t>
+          <t>Staking revenue received in cryptocurrencies</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" s="5" t="n">
-        <v>0.036572</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-8.175750000000001</v>
+        <v>-4.803686</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Provision for income tax (recovery) (note 22)</t>
+          <t>Realized gain on dispositions of cryptocurrencies</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" s="5" t="n">
-        <v>1.547686</v>
+        <v>-7.648448</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-1.6</v>
+        <v>-3.948587</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Income tax (recovery) expense</t>
+          <t>Realized (gain) loss on investments (note 9)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" s="5" t="n">
-        <v>1.584258</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>-9.77575</v>
+        <v>-1.160891</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Net (loss) income for the period (</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Unrealized (gain) loss on investments (note 9)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" s="5" t="n">
-        <v>6.607664</v>
+        <v>-1.064911</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>35.035126</v>
+        <v>0.000442</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Unrealized (loss) gain on cryptocurrencies (note 6)</t>
+          <t>Gain from dissolution of subsidiary after tax (note 19)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="5" t="n">
-        <v>3.733338</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>20.102436</v>
+        <v>-0.076096</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Deferred (tax) recovery on unrealized gain on cryptocurrencies (note 22)</t>
+          <t>Realized loss (gain) on sale of assets</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" s="5" t="n">
-        <v>-0.9959789999999999</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>-5.327145</v>
+        <v>0.021759</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Net (loss) income per share)</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Basic $</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Share-based compensation (notes 14 and 18)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
-        <v>3.5e-07</v>
+        <v>1.320919</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-1.74e-06</v>
+        <v>7.862418</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Net (loss) income per share)</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Diluted $</t>
+          <t>Interest paid with common shares</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" s="5" t="n">
-        <v>3.5e-07</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-1.74e-06</v>
+        <v>0.371891</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding)</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Basic 20,092,474</t>
+          <t>Accretion</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" s="5" t="n">
-        <v>8.64842</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>1e-06</v>
+        <v>1.489471</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Amortization (notes 7 and 8)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.031636</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>10.229862</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Impairment losses on intangible assets (note 7)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>27.561055</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" s="5" t="n">
+        <v>-0.003123</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>-0.12705</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss on convertible debt                                                     416,281</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Expenses paid in cryptocurrencies (note 6)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" s="5" t="n">
+        <v>-0.660317</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0.582302</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss on convertible debt                                                     416,281</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Income received in cryptocurrencies</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>-0.198994</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss on convertible debt                                                     416,281</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Deferred tax expense (recovery) (note 22)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" s="5" t="n">
+        <v>0.036572</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>-8.175750000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Net change in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Receivables and prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.110388</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>-0.160401</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Net change in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Income tax recoverable</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Net change in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.080433</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>2.084193</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Net change in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Income tax payable (note 22)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" s="5" t="n">
+        <v>1.547686</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>-1.547686</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Net change in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>-0.856729</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>-11.002868</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Proceeds from private placements for convertible debt</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Proceeds from convertible debt from ATW</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Proceeds from exercise of warrants</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>9.046670000000001</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Proceeds from exercise of options</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.170963</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>1.765033</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Credit facility proceeds (net)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>16.16459</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Purchase of shares for cancellation (note 10)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" s="5" t="n">
+        <v>-0.938924</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Cash used in financing activities</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>-0.767961</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>84.176293</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Purchase of intangible assets</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>-7.753192</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Purchase of cryptocurrencies (note 6)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" s="5" t="n">
+        <v>-19.690454</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>-74.920237</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Proceeds from sale of cryptocurrencies (note 6)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" s="5" t="n">
+        <v>14.012576</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>8.677327999999999</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Purchase of assets</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>-0.0272</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Proceeds from sale of assets</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" s="5" t="n">
+        <v>0.00675</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Sale/redemption of investments (note 9)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="5" t="n">
+        <v>7.17659</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.827227</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Cash provided by (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>1.505462</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>-73.196074</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Change in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>-0.119228</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>-0.022649</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>1.92728</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>1.808052</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents, end of the year $</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>1.808052</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>1.785403</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Validation service income - net (note 17) $</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>5.428188</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Staking rewards (note 17)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" s="5" t="n">
+        <v>0.271245</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>4.803686</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Realized (loss) gain on dispositions of cryptocurrencies (note 6)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" s="5" t="n">
+        <v>7.648448</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>3.948587</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Treasury management income</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.219775</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Dividend income</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>DividendIncome</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0.322362</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0.138398</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>0.148833</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.026213</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Realized (loss) gain on investments (note 9)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" s="5" t="n">
+        <v>1.160891</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>-0.000442</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Unrealized gain on investments (note 9)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" s="5" t="n">
+        <v>1.064911</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Gain from dissolution of subsidiary after tax (note 19)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" s="5" t="n">
+        <v>0.076096</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Realized loss on disposal of assets</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
+        <v>-0.021759</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Impairment losses on intangible assets (note 7)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>27.561055</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Amortization (note 7 and 8)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>0.031636</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>10.20773</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Share based compensation (notes 14 and 18)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" s="5" t="n">
+        <v>1.320919</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>7.862418</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Professional fees (note 18)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>0.323686</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>3.928001</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Interest expense and accretion</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>3.197059</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Transaction costs (note 12)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>2.380272</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Consulting fees (note 18)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>0.479493</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>1.796827</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0.853046</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>0.344096</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0.768085</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Listing fees</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0.5689689999999999</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>-0.050725</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0.163578</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Director fees (note 18)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0.088241</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>2.479105</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>59.375281</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>(Loss) income before taxes</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>8.191922</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>-44.810876</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Deferred tax expense (recovery) (note 22)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" s="5" t="n">
+        <v>0.036572</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>-8.175750000000001</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Provision for income tax (recovery) (note 22)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" s="5" t="n">
+        <v>1.547686</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Income tax (recovery) expense</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>1.584258</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>-9.77575</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Net (loss) income for the period</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>6.607664</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>-35.035126</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Unrealized (loss) gain on cryptocurrencies (note 6)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" s="5" t="n">
+        <v>3.733338</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>20.102436</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Deferred (tax) recovery on unrealized gain on cryptocurrencies (note 22)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" s="5" t="n">
+        <v>-0.9959789999999999</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>-5.327145</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Total comprehensive (loss) income $</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" s="5" t="n">
+        <v>9.345022999999999</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>-20.259835</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Net (loss) income per share)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Basic $</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" s="5" t="n">
+        <v>3.5e-07</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>-1.74e-06</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Net (loss) income per share)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Diluted $</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" s="5" t="n">
+        <v>3.5e-07</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>-1.74e-06</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
         <is>
           <t>Weighted average number of shares outstanding)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Diluted 20,092,474</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" s="5" t="n">
-        <v>8.748605</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>1e-06</v>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>18.64842</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>20.092474</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Diluted</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>18.748605</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>20.092474</v>
       </c>
     </row>
   </sheetData>

--- a/output/pdf_financials_xlsx/HODL.xlsx
+++ b/output/pdf_financials_xlsx/HODL.xlsx
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>17.297454</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>72.442431</v>
       </c>
     </row>
     <row r="93">
@@ -2736,7 +2736,11 @@
           <t>Reserves (notes 12, 14, 15 and 16)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>17.297454</v>
       </c>

--- a/output/pdf_financials_xlsx/HODL.xlsx
+++ b/output/pdf_financials_xlsx/HODL.xlsx
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.479493</v>
+        <v>0.509493</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2.649873</v>
+        <v>2.738114</v>
       </c>
     </row>
     <row r="8">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.149516</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.740472</v>
       </c>
     </row>
     <row r="68">
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>1.489471</v>
       </c>
     </row>
     <row r="111">
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-7.753192</v>
       </c>
     </row>
     <row r="117">
@@ -3134,7 +3134,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -3288,7 +3292,11 @@
           <t>Deferred tax expense (recovery) (note 22)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>0.036572</v>
       </c>
@@ -3632,7 +3640,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -4410,7 +4422,11 @@
           <t>Director fees (note 18)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="n">
         <v>0.03</v>
       </c>
@@ -4514,7 +4530,11 @@
           <t>Provision for income tax (recovery) (note 22)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="n">
         <v>1.547686</v>
       </c>
@@ -4538,7 +4558,11 @@
           <t>Income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E89" s="5" t="n">
         <v>1.584258</v>
       </c>
